--- a/docs/reports/连通标注_2026-07-04_分表/2_全球事件.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/2_全球事件.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K3" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1514,14 +1514,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K4" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K4" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>无 Event Registry API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (≈$600/月;免费2000token)</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K5" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K6" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1688,14 +1688,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K7" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K7" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(ACLED API)</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -1746,14 +1746,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K8" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K8" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>无 UCDP API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="K9" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K10" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="K11" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K12" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2036,14 +2036,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K13" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K13" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(ACLED API)</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="K14" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="K15" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K16" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2268,14 +2268,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K17" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K17" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(ACLED API)</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="K18" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="K19" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2442,14 +2442,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K20" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K20" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>无 RavenPack API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (机构,询价)</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K21" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="K22" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2616,14 +2616,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K23" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K23" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>无 RavenPack API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (机构,询价)</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="K24" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="K25" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
